--- a/data/trans_orig/P3A_R1-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P3A_R1-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente el/la entrevistado/a junto con su pareja en 2007</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada junto con su pareja en 2007 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>42926</t>
+          <t>41940</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>69675</t>
+          <t>69426</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27802</t>
+          <t>29334</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50708</t>
+          <t>52839</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>76625</t>
+          <t>76402</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>110524</t>
+          <t>111791</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,98%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>203335</t>
+          <t>203584</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>230084</t>
+          <t>231070</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>209116</t>
+          <t>206985</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>232022</t>
+          <t>230490</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>422310</t>
+          <t>421043</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>456209</t>
+          <t>456432</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,66%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>106249</t>
+          <t>104999</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>145826</t>
+          <t>144529</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>56459</t>
+          <t>56593</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>88082</t>
+          <t>87616</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>171681</t>
+          <t>169398</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>223862</t>
+          <t>220959</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,16%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>347249</t>
+          <t>348546</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>386826</t>
+          <t>388076</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>70,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>415867</t>
+          <t>416333</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>447490</t>
+          <t>447356</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>82,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>773162</t>
+          <t>776065</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>825343</t>
+          <t>827626</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>83,01%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47169</t>
+          <t>47375</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>75465</t>
+          <t>75477</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17833</t>
+          <t>18087</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37652</t>
+          <t>37788</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>68962</t>
+          <t>68946</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>104974</t>
+          <t>106019</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,2%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>243381</t>
+          <t>243369</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>271677</t>
+          <t>271471</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>297760</t>
+          <t>297624</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>317579</t>
+          <t>317325</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>549284</t>
+          <t>548239</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>585296</t>
+          <t>585312</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>59357</t>
+          <t>59011</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>90100</t>
+          <t>91202</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>54181</t>
+          <t>55734</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>83811</t>
+          <t>84101</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>122108</t>
+          <t>122086</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>163831</t>
+          <t>164157</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,52%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>268571</t>
+          <t>267469</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>299314</t>
+          <t>299660</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>286492</t>
+          <t>286202</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>316122</t>
+          <t>314569</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>565143</t>
+          <t>564817</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>606866</t>
+          <t>606888</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32345</t>
+          <t>31753</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>55114</t>
+          <t>55612</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14700</t>
+          <t>14250</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33423</t>
+          <t>32905</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>51033</t>
+          <t>51105</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>78892</t>
+          <t>81412</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,81%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>148194</t>
+          <t>147696</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>170963</t>
+          <t>171555</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>72,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>174245</t>
+          <t>174763</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>192968</t>
+          <t>193418</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>332084</t>
+          <t>329564</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>359943</t>
+          <t>359871</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,56%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>36057</t>
+          <t>36349</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>61333</t>
+          <t>61183</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>25719</t>
+          <t>25747</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>48307</t>
+          <t>48892</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>67767</t>
+          <t>67263</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>101665</t>
+          <t>102249</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,63%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>209478</t>
+          <t>209628</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>234754</t>
+          <t>234462</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>229837</t>
+          <t>229252</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>252425</t>
+          <t>252397</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>447290</t>
+          <t>446706</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>481188</t>
+          <t>481692</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,75%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>122867</t>
+          <t>122988</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>167145</t>
+          <t>166645</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>53490</t>
+          <t>53500</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>84002</t>
+          <t>85452</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>187144</t>
+          <t>185182</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>240543</t>
+          <t>238563</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,07%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>447882</t>
+          <t>448382</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>492160</t>
+          <t>492039</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>72,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>551833</t>
+          <t>550383</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>582345</t>
+          <t>582335</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1010319</t>
+          <t>1012299</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1063718</t>
+          <t>1065680</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>85,2%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>118807</t>
+          <t>116251</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>162336</t>
+          <t>162547</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>60485</t>
+          <t>59892</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>92784</t>
+          <t>93498</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>187793</t>
+          <t>182938</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>239243</t>
+          <t>240295</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,74%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>580577</t>
+          <t>580366</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>624106</t>
+          <t>626662</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>78,12%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>690727</t>
+          <t>690013</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>723026</t>
+          <t>723619</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1287181</t>
+          <t>1286129</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1338631</t>
+          <t>1343486</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>88,02%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>635310</t>
+          <t>640571</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>729493</t>
+          <t>736856</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>367940</t>
+          <t>371045</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>443267</t>
+          <t>445792</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1031181</t>
+          <t>1029471</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1145058</t>
+          <t>1154499</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,36%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2546168</t>
+          <t>2538805</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2640351</t>
+          <t>2635090</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2931378</t>
+          <t>2928853</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3006705</t>
+          <t>3003600</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5505249</t>
+          <t>5495808</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5619126</t>
+          <t>5620836</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>84,52%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente el/la entrevistado/a junto con su pareja en 2012</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada junto con su pareja en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>71763</t>
+          <t>68895</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>106593</t>
+          <t>102970</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16311</t>
+          <t>16806</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36794</t>
+          <t>36732</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>92979</t>
+          <t>93967</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>133905</t>
+          <t>133437</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,93%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>188145</t>
+          <t>191768</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>222975</t>
+          <t>225843</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>65,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>250451</t>
+          <t>250513</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>270934</t>
+          <t>270439</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>448078</t>
+          <t>448546</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>489004</t>
+          <t>488016</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>83,85%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>103533</t>
+          <t>103762</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>145213</t>
+          <t>143181</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>53187</t>
+          <t>50814</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>85117</t>
+          <t>86872</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>165221</t>
+          <t>164720</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>218192</t>
+          <t>217491</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,15%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>359255</t>
+          <t>361287</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>400935</t>
+          <t>400706</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>71,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>79,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>438648</t>
+          <t>436893</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>470578</t>
+          <t>472951</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>810041</t>
+          <t>810742</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>863012</t>
+          <t>863513</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>83,98%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>66993</t>
+          <t>67165</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>99228</t>
+          <t>98040</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25221</t>
+          <t>24189</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48768</t>
+          <t>49818</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>100915</t>
+          <t>99994</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>138165</t>
+          <t>139324</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,95%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>224818</t>
+          <t>226006</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>257053</t>
+          <t>256881</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>292252</t>
+          <t>291202</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>315799</t>
+          <t>316831</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>526901</t>
+          <t>525742</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>564151</t>
+          <t>565072</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>79,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>84,96%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>93232</t>
+          <t>93403</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>131581</t>
+          <t>130589</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36055</t>
+          <t>36533</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>62435</t>
+          <t>63359</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>138183</t>
+          <t>137609</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>183344</t>
+          <t>183836</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,1%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>242401</t>
+          <t>243393</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>280750</t>
+          <t>280579</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>326516</t>
+          <t>325592</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>352896</t>
+          <t>352418</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>579589</t>
+          <t>579097</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>624750</t>
+          <t>625324</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>75,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>81,96%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28776</t>
+          <t>29623</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>53268</t>
+          <t>52754</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,82 +5443,82 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>13,93%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>24,81%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>33006</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>23915</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>44286</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>15,03%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>10,89%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>20,17%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>73005</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>58473</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>89687</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>16,89%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>13,53%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>25,05%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>33006</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>22743</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>43856</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>15,03%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>10,36%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>19,97%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>73005</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>58742</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>90369</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>16,89%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>13,59%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,75%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>159350</t>
+          <t>159864</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>183842</t>
+          <t>182995</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,82 +5556,82 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>75,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
+          <t>86,07%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>186585</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>175305</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>195676</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>84,97%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>79,83%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>89,11%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>359204</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>342522</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>373736</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>83,11%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>79,25%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t>86,47%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>186585</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>175735</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>196848</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>84,97%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>80,03%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>89,64%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>337</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>359204</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>341840</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>373467</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>83,11%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>79,09%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>86,41%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>67975</t>
+          <t>65543</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>98878</t>
+          <t>99318</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>39150</t>
+          <t>39431</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>65289</t>
+          <t>67552</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>113735</t>
+          <t>112501</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>156655</t>
+          <t>155293</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,03%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>175103</t>
+          <t>174663</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>206006</t>
+          <t>208438</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>214742</t>
+          <t>212479</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>240881</t>
+          <t>240600</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>75,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>397357</t>
+          <t>398719</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>440277</t>
+          <t>441511</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,72%</t>
+          <t>71,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,69%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>157939</t>
+          <t>158231</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>206257</t>
+          <t>208246</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>102960</t>
+          <t>102849</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>144796</t>
+          <t>145062</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>276536</t>
+          <t>274663</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>340038</t>
+          <t>335323</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>24,72%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>456531</t>
+          <t>454542</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>504849</t>
+          <t>504557</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>68,58%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>549057</t>
+          <t>548791</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>590893</t>
+          <t>591004</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>79,09%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1016603</t>
+          <t>1021318</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1080105</t>
+          <t>1081978</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>79,75%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>207953</t>
+          <t>206787</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>261822</t>
+          <t>261125</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>119456</t>
+          <t>120199</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>165367</t>
+          <t>165644</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>338694</t>
+          <t>342880</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>410267</t>
+          <t>415827</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,97%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>517276</t>
+          <t>517973</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>571145</t>
+          <t>572311</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>66,39%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>656485</t>
+          <t>656208</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>702396</t>
+          <t>701653</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1190683</t>
+          <t>1185123</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1262256</t>
+          <t>1258070</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>74,03%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>78,58%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>886882</t>
+          <t>885148</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>993468</t>
+          <t>996643</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>482746</t>
+          <t>487569</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>572044</t>
+          <t>570891</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1397854</t>
+          <t>1400238</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1539790</t>
+          <t>1548024</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,17%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2432251</t>
+          <t>2429076</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2538837</t>
+          <t>2540571</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2984264</t>
+          <t>2985417</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3073562</t>
+          <t>3068739</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5442237</t>
+          <t>5434003</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5584173</t>
+          <t>5581789</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>79,95%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente el/la entrevistado/a junto con su pareja en 2016</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada junto con su pareja en 2016 (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>74992</t>
+          <t>75255</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>109285</t>
+          <t>109637</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28127</t>
+          <t>28888</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>52755</t>
+          <t>52408</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>111321</t>
+          <t>109042</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>153522</t>
+          <t>150883</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>25,9%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>184476</t>
+          <t>184124</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>218769</t>
+          <t>218506</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>74,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>235948</t>
+          <t>236295</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>260576</t>
+          <t>259815</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>428942</t>
+          <t>431581</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>471143</t>
+          <t>473422</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>81,28%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>126580</t>
+          <t>124199</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>167967</t>
+          <t>168103</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>66921</t>
+          <t>66147</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>102493</t>
+          <t>98814</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>204408</t>
+          <t>201964</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>258237</t>
+          <t>254614</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>24,94%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>330892</t>
+          <t>330756</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>372279</t>
+          <t>374660</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,33%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>75,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>419657</t>
+          <t>423336</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>455229</t>
+          <t>456003</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>762772</t>
+          <t>766395</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>816601</t>
+          <t>819045</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>75,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>80,22%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>112382</t>
+          <t>111742</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>145605</t>
+          <t>146178</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>59422</t>
+          <t>60725</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>91271</t>
+          <t>91434</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>177441</t>
+          <t>181023</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>227313</t>
+          <t>228990</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>35,01%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>172224</t>
+          <t>171651</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>205447</t>
+          <t>206087</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>245038</t>
+          <t>244875</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>276887</t>
+          <t>275584</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>72,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>426825</t>
+          <t>425148</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>476697</t>
+          <t>473115</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>64,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>72,33%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>98798</t>
+          <t>99270</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>135179</t>
+          <t>136456</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38249</t>
+          <t>38400</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65184</t>
+          <t>66325</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>145315</t>
+          <t>146457</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>193193</t>
+          <t>193190</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,7 +8493,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>232881</t>
+          <t>231604</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>269262</t>
+          <t>268790</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>62,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>322099</t>
+          <t>320958</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>349034</t>
+          <t>348883</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>562150</t>
+          <t>562153</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>610028</t>
+          <t>608886</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8611,7 +8611,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,61%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>61993</t>
+          <t>63065</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>90219</t>
+          <t>90728</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29780</t>
+          <t>29658</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>51982</t>
+          <t>52438</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>97874</t>
+          <t>99627</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>137094</t>
+          <t>135657</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>31,63%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>121002</t>
+          <t>120493</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>149228</t>
+          <t>148156</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>57,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>70,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>165651</t>
+          <t>165195</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>187853</t>
+          <t>187975</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>291760</t>
+          <t>293197</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>330980</t>
+          <t>329227</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>68,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>76,77%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>52395</t>
+          <t>52581</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>81134</t>
+          <t>81784</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22056</t>
+          <t>22048</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>42937</t>
+          <t>43582</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>79765</t>
+          <t>79895</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>115986</t>
+          <t>117065</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,94%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>180355</t>
+          <t>179705</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>209094</t>
+          <t>208908</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>68,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>229137</t>
+          <t>228492</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>250018</t>
+          <t>250026</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>417577</t>
+          <t>416498</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>453798</t>
+          <t>453668</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>78,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>85,03%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>167229</t>
+          <t>161502</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>215340</t>
+          <t>212311</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>138519</t>
+          <t>138010</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>182829</t>
+          <t>180688</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>315867</t>
+          <t>317327</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>381431</t>
+          <t>383273</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,5%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>440168</t>
+          <t>443197</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>488279</t>
+          <t>494006</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>67,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>506433</t>
+          <t>508574</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>550743</t>
+          <t>551252</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>73,47%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>963339</t>
+          <t>961497</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1028903</t>
+          <t>1027443</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>71,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,4%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>251284</t>
+          <t>253644</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>307049</t>
+          <t>307319</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>156438</t>
+          <t>157594</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>203761</t>
+          <t>204161</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>424774</t>
+          <t>425627</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>497314</t>
+          <t>495660</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>30,89%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>471534</t>
+          <t>471264</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>527299</t>
+          <t>524939</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>60,53%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>67,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>622406</t>
+          <t>622006</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>669729</t>
+          <t>668573</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>75,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1107436</t>
+          <t>1109090</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1179976</t>
+          <t>1179123</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>69,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>73,53%</t>
+          <t>73,48%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1044449</t>
+          <t>1039782</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1158096</t>
+          <t>1155736</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>611538</t>
+          <t>610279</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>706442</t>
+          <t>703337</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1674992</t>
+          <t>1676119</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1826342</t>
+          <t>1828966</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,41%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2227213</t>
+          <t>2229573</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2340860</t>
+          <t>2345527</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2833138</t>
+          <t>2836243</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2928042</t>
+          <t>2929301</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5098548</t>
+          <t>5095924</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5249898</t>
+          <t>5248771</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>75,8%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente el/la entrevistado/a junto con su pareja en 2023</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada junto con su pareja en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>60182</t>
+          <t>62694</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>94411</t>
+          <t>94244</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>65639</t>
+          <t>64989</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>91440</t>
+          <t>90416</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>133821</t>
+          <t>135184</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>175045</t>
+          <t>175178</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,14%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>217032</t>
+          <t>217199</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>251261</t>
+          <t>248749</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>198195</t>
+          <t>199219</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>223996</t>
+          <t>224646</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,43%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>426032</t>
+          <t>425899</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>467256</t>
+          <t>465893</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>77,51%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>179957</t>
+          <t>180391</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>237616</t>
+          <t>237390</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>140429</t>
+          <t>140027</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>175907</t>
+          <t>177113</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>331284</t>
+          <t>333121</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>399349</t>
+          <t>399678</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,68%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>280774</t>
+          <t>281000</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>338433</t>
+          <t>337999</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>54,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,29%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>339062</t>
+          <t>337856</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>374540</t>
+          <t>374942</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>65,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>72,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>634010</t>
+          <t>633681</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>702075</t>
+          <t>700238</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>61,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>67,76%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>89898</t>
+          <t>88559</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>120116</t>
+          <t>120478</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>84802</t>
+          <t>84964</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>113464</t>
+          <t>113820</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>180734</t>
+          <t>183896</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>225080</t>
+          <t>224717</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>33,88%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>195302</t>
+          <t>194940</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>225520</t>
+          <t>226859</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>61,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>234404</t>
+          <t>234048</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>263066</t>
+          <t>262904</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>438206</t>
+          <t>438569</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>482552</t>
+          <t>479390</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>66,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>72,28%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>81889</t>
+          <t>81245</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>122425</t>
+          <t>121159</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40896</t>
+          <t>43141</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>90340</t>
+          <t>90449</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>122586</t>
+          <t>121410</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>205941</t>
+          <t>203012</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>25,75%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>190132</t>
+          <t>191398</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>230668</t>
+          <t>231312</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,83%</t>
+          <t>61,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>385378</t>
+          <t>385269</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>434822</t>
+          <t>432577</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>80,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>582333</t>
+          <t>585262</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>665688</t>
+          <t>666864</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>74,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,6%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32710</t>
+          <t>33277</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>51688</t>
+          <t>51357</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23886</t>
+          <t>25661</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>60860</t>
+          <t>62827</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>56569</t>
+          <t>59748</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>104969</t>
+          <t>106948</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,47%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>126587</t>
+          <t>126918</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>145565</t>
+          <t>144998</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>197919</t>
+          <t>195952</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>234893</t>
+          <t>233118</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>332086</t>
+          <t>330107</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>380486</t>
+          <t>377307</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>86,33%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>92723</t>
+          <t>92266</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>123438</t>
+          <t>122737</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>83232</t>
+          <t>84746</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>108378</t>
+          <t>109064</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>184306</t>
+          <t>186214</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>222315</t>
+          <t>222961</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>42,33%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>146198</t>
+          <t>146899</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>176913</t>
+          <t>177370</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>148678</t>
+          <t>147992</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>173824</t>
+          <t>172310</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>57,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>304377</t>
+          <t>303731</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>342386</t>
+          <t>340478</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>57,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>64,64%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>152281</t>
+          <t>149464</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>199028</t>
+          <t>197972</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>81756</t>
+          <t>78233</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>210953</t>
+          <t>210099</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>202956</t>
+          <t>212344</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>393207</t>
+          <t>391704</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,58%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>425251</t>
+          <t>426307</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>471998</t>
+          <t>474815</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>68,12%</t>
+          <t>68,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>638312</t>
+          <t>639166</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>767509</t>
+          <t>771032</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>75,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1080337</t>
+          <t>1081840</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1270588</t>
+          <t>1261200</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>85,59%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>49714</t>
+          <t>50961</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>167959</t>
+          <t>165997</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>27725</t>
+          <t>27615</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>45701</t>
+          <t>46736</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>96421</t>
+          <t>97086</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>189338</t>
+          <t>191103</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,61%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>760761</t>
+          <t>762723</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>879006</t>
+          <t>877759</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>672030</t>
+          <t>670995</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>690006</t>
+          <t>690116</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1457114</t>
+          <t>1455349</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1550031</t>
+          <t>1549366</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,1%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>732759</t>
+          <t>734467</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1022406</t>
+          <t>1027734</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>604305</t>
+          <t>592589</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>803283</t>
+          <t>809525</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1448600</t>
+          <t>1453819</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1794625</t>
+          <t>1803776</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,16%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2436312</t>
+          <t>2430984</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2725959</t>
+          <t>2724251</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2907737</t>
+          <t>2901495</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3106715</t>
+          <t>3118431</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5375113</t>
+          <t>5365962</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5721138</t>
+          <t>5715919</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>79,72%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P3A_R1-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P3A_R1-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>41940</t>
+          <t>41187</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>69426</t>
+          <t>68649</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29334</t>
+          <t>28276</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>52839</t>
+          <t>51535</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>76402</t>
+          <t>76137</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>111791</t>
+          <t>111666</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,96%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>203584</t>
+          <t>204361</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>231070</t>
+          <t>231823</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>206985</t>
+          <t>208289</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>230490</t>
+          <t>231548</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>80,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>421043</t>
+          <t>421168</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>456432</t>
+          <t>456697</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>85,71%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>104999</t>
+          <t>106596</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>144529</t>
+          <t>147918</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>56593</t>
+          <t>55988</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>87616</t>
+          <t>87253</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>169398</t>
+          <t>172435</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>220959</t>
+          <t>220435</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,11%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>348546</t>
+          <t>345157</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>388076</t>
+          <t>386479</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>70,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>416333</t>
+          <t>416696</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>447356</t>
+          <t>447961</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>776065</t>
+          <t>776589</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>827626</t>
+          <t>824589</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>82,71%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47375</t>
+          <t>45439</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>75477</t>
+          <t>75887</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18087</t>
+          <t>16644</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37788</t>
+          <t>36126</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>68946</t>
+          <t>69417</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>106019</t>
+          <t>105737</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,16%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>243369</t>
+          <t>242959</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>271471</t>
+          <t>273407</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>76,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>297624</t>
+          <t>299286</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>317325</t>
+          <t>318768</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>548239</t>
+          <t>548521</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>585312</t>
+          <t>584841</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,39%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>59011</t>
+          <t>59579</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>91202</t>
+          <t>89935</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55734</t>
+          <t>55574</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>84101</t>
+          <t>84251</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>122086</t>
+          <t>120854</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>164157</t>
+          <t>163986</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,5%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>267469</t>
+          <t>268736</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>299660</t>
+          <t>299092</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>286202</t>
+          <t>286052</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>314569</t>
+          <t>314729</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>564817</t>
+          <t>564988</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>606888</t>
+          <t>608120</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>83,42%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31753</t>
+          <t>29798</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>55612</t>
+          <t>53609</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14250</t>
+          <t>14249</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32905</t>
+          <t>32020</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>51105</t>
+          <t>51407</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>81412</t>
+          <t>79479</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,34%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>147696</t>
+          <t>149699</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>171555</t>
+          <t>173510</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>73,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>174763</t>
+          <t>175648</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>193418</t>
+          <t>193419</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>329564</t>
+          <t>331497</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>359871</t>
+          <t>359569</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,49%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>36349</t>
+          <t>35475</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>61183</t>
+          <t>61289</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>25747</t>
+          <t>26032</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>48892</t>
+          <t>47556</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>67263</t>
+          <t>68411</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>102249</t>
+          <t>100270</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,27%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>209628</t>
+          <t>209522</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>234462</t>
+          <t>235336</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>77,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>229252</t>
+          <t>230588</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>252397</t>
+          <t>252112</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>446706</t>
+          <t>448685</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>481692</t>
+          <t>480544</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,54%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>122988</t>
+          <t>123715</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>166645</t>
+          <t>165328</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>53500</t>
+          <t>53532</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>85452</t>
+          <t>84427</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>185182</t>
+          <t>186615</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>238563</t>
+          <t>238845</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,09%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>448382</t>
+          <t>449699</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>492039</t>
+          <t>491312</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>550383</t>
+          <t>551408</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>582335</t>
+          <t>582303</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1012299</t>
+          <t>1012017</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1065680</t>
+          <t>1064247</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>85,08%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>116251</t>
+          <t>116285</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>162547</t>
+          <t>160192</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>59892</t>
+          <t>60283</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>93498</t>
+          <t>92791</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>182938</t>
+          <t>186053</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>240295</t>
+          <t>240150</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,73%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>580366</t>
+          <t>582721</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>626662</t>
+          <t>626628</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>690013</t>
+          <t>690720</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>723619</t>
+          <t>723228</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1286129</t>
+          <t>1286274</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1343486</t>
+          <t>1340371</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>87,81%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>640571</t>
+          <t>639436</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>736856</t>
+          <t>734655</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>371045</t>
+          <t>367576</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>445792</t>
+          <t>444153</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1029471</t>
+          <t>1027807</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1154499</t>
+          <t>1148678</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,27%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2538805</t>
+          <t>2541006</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2635090</t>
+          <t>2636225</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2928853</t>
+          <t>2930492</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3003600</t>
+          <t>3007069</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5495808</t>
+          <t>5501629</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5620836</t>
+          <t>5622500</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,54%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>68895</t>
+          <t>69689</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>102970</t>
+          <t>103300</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16806</t>
+          <t>16952</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36732</t>
+          <t>38014</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>93967</t>
+          <t>93238</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>133437</t>
+          <t>134140</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>23,05%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>191768</t>
+          <t>191438</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>225843</t>
+          <t>225049</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>64,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>250513</t>
+          <t>249231</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>270439</t>
+          <t>270293</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>448546</t>
+          <t>447843</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>488016</t>
+          <t>488745</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>83,98%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>103762</t>
+          <t>103430</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>143181</t>
+          <t>141377</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>50814</t>
+          <t>52455</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>86872</t>
+          <t>85477</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>164720</t>
+          <t>167704</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>217491</t>
+          <t>218428</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,24%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>361287</t>
+          <t>363091</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>400706</t>
+          <t>401038</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,62%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>79,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>436893</t>
+          <t>438288</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>472951</t>
+          <t>471310</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>810742</t>
+          <t>809805</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>863513</t>
+          <t>860529</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>83,69%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>67165</t>
+          <t>68459</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>98040</t>
+          <t>98674</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24189</t>
+          <t>24698</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49818</t>
+          <t>49398</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>99994</t>
+          <t>99851</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>139324</t>
+          <t>140053</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,06%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>226006</t>
+          <t>225372</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>256881</t>
+          <t>255587</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>291202</t>
+          <t>291622</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>316831</t>
+          <t>316322</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>525742</t>
+          <t>525013</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>565072</t>
+          <t>565215</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>84,99%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>93403</t>
+          <t>91976</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>130589</t>
+          <t>130132</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36533</t>
+          <t>36715</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>63359</t>
+          <t>64001</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>137609</t>
+          <t>138032</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>183836</t>
+          <t>184873</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,23%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>243393</t>
+          <t>243850</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>280579</t>
+          <t>282006</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>325592</t>
+          <t>324950</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>352418</t>
+          <t>352236</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>579097</t>
+          <t>578060</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>625324</t>
+          <t>624901</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>81,91%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29623</t>
+          <t>30232</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>52754</t>
+          <t>52337</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23915</t>
+          <t>23333</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44286</t>
+          <t>44721</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>58473</t>
+          <t>59197</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>89687</t>
+          <t>90270</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,89%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>159864</t>
+          <t>160281</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>182995</t>
+          <t>182386</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>175305</t>
+          <t>174870</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>195676</t>
+          <t>196258</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>342522</t>
+          <t>341939</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>373736</t>
+          <t>373012</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,3%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>65543</t>
+          <t>69283</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>99318</t>
+          <t>99893</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>39431</t>
+          <t>39410</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>67552</t>
+          <t>65424</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>112501</t>
+          <t>114064</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>155293</t>
+          <t>157664</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,46%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>174663</t>
+          <t>174088</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>208438</t>
+          <t>204698</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>212479</t>
+          <t>214607</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>240600</t>
+          <t>240621</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,88%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>398719</t>
+          <t>396348</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>441511</t>
+          <t>439948</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>79,41%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>158231</t>
+          <t>159304</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>208246</t>
+          <t>207366</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>102849</t>
+          <t>101660</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>145062</t>
+          <t>147076</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>274663</t>
+          <t>273514</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>335323</t>
+          <t>335473</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,73%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>454542</t>
+          <t>455422</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>504557</t>
+          <t>503484</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>68,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>75,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>548791</t>
+          <t>546777</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>591004</t>
+          <t>592193</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1021318</t>
+          <t>1021168</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1081978</t>
+          <t>1083127</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>79,84%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>206787</t>
+          <t>206000</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>261125</t>
+          <t>259945</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>120199</t>
+          <t>119986</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>165644</t>
+          <t>162951</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>342880</t>
+          <t>337162</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>415827</t>
+          <t>405732</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>25,34%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>517973</t>
+          <t>519153</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>572311</t>
+          <t>573098</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>66,48%</t>
+          <t>66,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>73,46%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>656208</t>
+          <t>658901</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>701653</t>
+          <t>701866</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>80,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1185123</t>
+          <t>1195218</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1258070</t>
+          <t>1263788</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,94%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>885148</t>
+          <t>883601</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>996643</t>
+          <t>998295</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>487569</t>
+          <t>489634</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>570891</t>
+          <t>579077</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1400238</t>
+          <t>1403293</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1548024</t>
+          <t>1543968</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,11%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2429076</t>
+          <t>2427424</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2540571</t>
+          <t>2542118</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>74,21%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2985417</t>
+          <t>2977231</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3068739</t>
+          <t>3066674</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5434003</t>
+          <t>5438059</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5581789</t>
+          <t>5578734</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>79,9%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>75255</t>
+          <t>74388</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>109637</t>
+          <t>108399</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28888</t>
+          <t>27712</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>52408</t>
+          <t>53326</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>109042</t>
+          <t>109858</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>150883</t>
+          <t>152071</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>26,11%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>184124</t>
+          <t>185362</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>218506</t>
+          <t>219373</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>63,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>74,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>236295</t>
+          <t>235377</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>259815</t>
+          <t>260991</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>431581</t>
+          <t>430393</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>473422</t>
+          <t>472606</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>81,14%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>124199</t>
+          <t>127608</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>168103</t>
+          <t>166762</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>66147</t>
+          <t>65193</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>98814</t>
+          <t>99185</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>201964</t>
+          <t>204435</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>254614</t>
+          <t>255240</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,0%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>330756</t>
+          <t>332097</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>374660</t>
+          <t>371251</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>66,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>74,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>423336</t>
+          <t>422965</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>456003</t>
+          <t>456957</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>766395</t>
+          <t>765769</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>819045</t>
+          <t>816574</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>79,98%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>111742</t>
+          <t>111398</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>146178</t>
+          <t>144735</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>60725</t>
+          <t>59884</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>91434</t>
+          <t>90658</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>181023</t>
+          <t>178595</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>228990</t>
+          <t>225962</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>34,54%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>171651</t>
+          <t>173094</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>206087</t>
+          <t>206431</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>54,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>64,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>244875</t>
+          <t>245651</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>275584</t>
+          <t>276425</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>425148</t>
+          <t>428176</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>473115</t>
+          <t>475543</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>72,7%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>99270</t>
+          <t>98760</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>136456</t>
+          <t>137888</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38400</t>
+          <t>38638</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66325</t>
+          <t>66689</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>146457</t>
+          <t>145379</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>193190</t>
+          <t>191763</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,39%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>231604</t>
+          <t>230172</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>268790</t>
+          <t>269300</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>62,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>73,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>320958</t>
+          <t>320594</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>348883</t>
+          <t>348645</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>562153</t>
+          <t>563580</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>608886</t>
+          <t>609964</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>74,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>80,75%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>63065</t>
+          <t>62218</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>90728</t>
+          <t>90252</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29658</t>
+          <t>30420</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>52438</t>
+          <t>52884</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>99627</t>
+          <t>99659</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>135657</t>
+          <t>135875</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,68%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>120493</t>
+          <t>120969</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>148156</t>
+          <t>149003</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>57,05%</t>
+          <t>57,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,14%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>165195</t>
+          <t>164749</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>187975</t>
+          <t>187213</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>75,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>293197</t>
+          <t>292979</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>329227</t>
+          <t>329195</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,76%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>52581</t>
+          <t>53035</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>81784</t>
+          <t>81321</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22048</t>
+          <t>22495</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>43582</t>
+          <t>43648</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>79895</t>
+          <t>81005</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>117065</t>
+          <t>116590</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,85%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>179705</t>
+          <t>180168</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>208908</t>
+          <t>208454</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>228492</t>
+          <t>228426</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>250026</t>
+          <t>249579</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>416498</t>
+          <t>416973</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>453668</t>
+          <t>452558</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>84,82%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>161502</t>
+          <t>167616</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>212311</t>
+          <t>215108</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>138010</t>
+          <t>136563</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>180688</t>
+          <t>179750</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>317327</t>
+          <t>313347</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>383273</t>
+          <t>381499</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,37%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>443197</t>
+          <t>440400</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>494006</t>
+          <t>487892</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>67,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>508574</t>
+          <t>509512</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>551252</t>
+          <t>552699</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>961497</t>
+          <t>963271</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1027443</t>
+          <t>1031423</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>76,7%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>253644</t>
+          <t>255819</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>307319</t>
+          <t>308874</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>157594</t>
+          <t>158146</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>204161</t>
+          <t>205709</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>425627</t>
+          <t>424934</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>495660</t>
+          <t>498476</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>31,06%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>471264</t>
+          <t>469709</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>524939</t>
+          <t>522764</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>60,33%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>622006</t>
+          <t>620458</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>668573</t>
+          <t>668021</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>75,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>80,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1109090</t>
+          <t>1106274</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1179123</t>
+          <t>1179816</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>68,94%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>73,52%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1039782</t>
+          <t>1046073</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1155736</t>
+          <t>1157803</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>610279</t>
+          <t>608342</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>703337</t>
+          <t>703798</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1676119</t>
+          <t>1681725</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1828966</t>
+          <t>1826660</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,38%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2229573</t>
+          <t>2227506</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2345527</t>
+          <t>2339236</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>69,1%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2836243</t>
+          <t>2835782</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2929301</t>
+          <t>2931238</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5095924</t>
+          <t>5098230</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5248771</t>
+          <t>5243165</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>73,62%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>75,71%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>77469</t>
+          <t>78763</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>62694</t>
+          <t>63512</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>94244</t>
+          <t>94837</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>77364</t>
+          <t>77424</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>64989</t>
+          <t>65978</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>90416</t>
+          <t>89932</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>154833</t>
+          <t>156187</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>135184</t>
+          <t>137902</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>175178</t>
+          <t>177455</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>27,95%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>233974</t>
+          <t>240082</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>217199</t>
+          <t>224008</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>248749</t>
+          <t>255333</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>70,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>80,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>212271</t>
+          <t>238637</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>199219</t>
+          <t>226129</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>224646</t>
+          <t>250083</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>446244</t>
+          <t>478719</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>425899</t>
+          <t>457451</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>465893</t>
+          <t>497004</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>74,24%</t>
+          <t>75,4%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>78,28%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>208941</t>
+          <t>221507</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>180391</t>
+          <t>193835</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>237390</t>
+          <t>248336</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>157180</t>
+          <t>170208</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>140027</t>
+          <t>149806</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>177113</t>
+          <t>191211</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>366121</t>
+          <t>391715</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>333121</t>
+          <t>356307</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>399678</t>
+          <t>427538</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>39,69%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>309449</t>
+          <t>309140</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>281000</t>
+          <t>282311</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>337999</t>
+          <t>336812</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>59,69%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54,21%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>357789</t>
+          <t>376286</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>337856</t>
+          <t>355283</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>374942</t>
+          <t>396688</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>69,48%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>667238</t>
+          <t>685426</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>633681</t>
+          <t>649603</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>700238</t>
+          <t>720834</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>63,63%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>66,92%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>104026</t>
+          <t>102049</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>88559</t>
+          <t>86074</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>120478</t>
+          <t>118741</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>98969</t>
+          <t>103749</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>84964</t>
+          <t>88598</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>113820</t>
+          <t>116891</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>202995</t>
+          <t>205798</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>183896</t>
+          <t>185286</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>224717</t>
+          <t>227315</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>33,9%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>211392</t>
+          <t>213335</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>194940</t>
+          <t>196643</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>226859</t>
+          <t>229310</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>72,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>248899</t>
+          <t>251387</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>234048</t>
+          <t>238245</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>262904</t>
+          <t>266538</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>67,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>75,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>460291</t>
+          <t>464722</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>438569</t>
+          <t>443205</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>479390</t>
+          <t>485234</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>69,31%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>72,37%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>315418</t>
+          <t>315384</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>315418</t>
+          <t>315384</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>315418</t>
+          <t>315384</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>347868</t>
+          <t>355136</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>347868</t>
+          <t>355136</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>347868</t>
+          <t>355136</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>663286</t>
+          <t>670520</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>663286</t>
+          <t>670520</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>663286</t>
+          <t>670520</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>101257</t>
+          <t>118111</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>81245</t>
+          <t>94602</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>121159</t>
+          <t>143306</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>69194</t>
+          <t>77723</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43141</t>
+          <t>63153</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>90449</t>
+          <t>91386</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>170451</t>
+          <t>195834</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>121410</t>
+          <t>168258</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>203012</t>
+          <t>226159</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>28,44%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>211300</t>
+          <t>255034</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>191398</t>
+          <t>229839</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>231312</t>
+          <t>278543</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>68,35%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>61,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>406524</t>
+          <t>344238</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>385269</t>
+          <t>330575</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>432577</t>
+          <t>358808</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>617823</t>
+          <t>599273</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>585262</t>
+          <t>568948</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>666864</t>
+          <t>626849</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>75,37%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>78,84%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>41625</t>
+          <t>48120</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33277</t>
+          <t>38053</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>51357</t>
+          <t>58910</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>47515</t>
+          <t>51282</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25661</t>
+          <t>43053</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>62827</t>
+          <t>59879</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>89140</t>
+          <t>99403</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>59748</t>
+          <t>86164</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>106948</t>
+          <t>112968</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>26,02%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>136650</t>
+          <t>157061</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>126918</t>
+          <t>146271</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>144998</t>
+          <t>167128</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>76,55%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>71,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>211264</t>
+          <t>177636</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>195952</t>
+          <t>169039</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>233118</t>
+          <t>185865</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>347915</t>
+          <t>334696</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>330107</t>
+          <t>321131</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>377307</t>
+          <t>347935</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>77,1%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>73,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>80,15%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178275</t>
+          <t>205181</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178275</t>
+          <t>205181</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178275</t>
+          <t>205181</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>437055</t>
+          <t>434099</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>437055</t>
+          <t>434099</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>437055</t>
+          <t>434099</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>108544</t>
+          <t>110107</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>92266</t>
+          <t>95087</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>122737</t>
+          <t>124023</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>95534</t>
+          <t>96874</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>84746</t>
+          <t>84638</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>109064</t>
+          <t>109500</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>204078</t>
+          <t>206981</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>186214</t>
+          <t>189340</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>222961</t>
+          <t>225895</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>42,27%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>161092</t>
+          <t>160600</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>146899</t>
+          <t>146684</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>177370</t>
+          <t>175620</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>59,74%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>54,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>161522</t>
+          <t>166876</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>147992</t>
+          <t>154250</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>172310</t>
+          <t>179112</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>63,27%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>58,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,03%</t>
+          <t>67,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>322614</t>
+          <t>327476</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>303731</t>
+          <t>308562</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>340478</t>
+          <t>345117</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>64,57%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>174609</t>
+          <t>210694</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>149464</t>
+          <t>184519</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>197972</t>
+          <t>237832</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>153210</t>
+          <t>177953</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>78233</t>
+          <t>159425</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>210099</t>
+          <t>200730</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>327819</t>
+          <t>388647</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>212344</t>
+          <t>357844</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>391704</t>
+          <t>421726</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>28,27%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>449670</t>
+          <t>508993</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>426307</t>
+          <t>481855</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>474815</t>
+          <t>535168</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>70,72%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>74,36%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>696055</t>
+          <t>594104</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>639166</t>
+          <t>571327</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>771032</t>
+          <t>612632</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>79,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1145725</t>
+          <t>1103097</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1081840</t>
+          <t>1070018</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1261200</t>
+          <t>1133900</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>71,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>76,01%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>115759</t>
+          <t>135909</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>50961</t>
+          <t>114804</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>165997</t>
+          <t>157020</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>36363</t>
+          <t>41806</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>27615</t>
+          <t>31352</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>46736</t>
+          <t>53240</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>152122</t>
+          <t>177715</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>97086</t>
+          <t>151080</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>191103</t>
+          <t>201444</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>12,36%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>812961</t>
+          <t>662163</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>762723</t>
+          <t>641052</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>877759</t>
+          <t>683268</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>681368</t>
+          <t>789525</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>670995</t>
+          <t>778091</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>690116</t>
+          <t>799979</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1494330</t>
+          <t>1451688</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1455349</t>
+          <t>1427959</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1549366</t>
+          <t>1478323</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>90,73%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>932230</t>
+          <t>1025259</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>734467</t>
+          <t>964591</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1027734</t>
+          <t>1085978</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>735328</t>
+          <t>797020</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>592589</t>
+          <t>750751</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>809525</t>
+          <t>837236</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1667558</t>
+          <t>1822280</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1453819</t>
+          <t>1744970</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1803776</t>
+          <t>1897108</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>26,1%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2526488</t>
+          <t>2506410</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2430984</t>
+          <t>2445691</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2724251</t>
+          <t>2567078</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>70,97%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>69,25%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>72,69%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2975692</t>
+          <t>2938689</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2901495</t>
+          <t>2898473</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3118431</t>
+          <t>2984958</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>5502180</t>
+          <t>5445098</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5365962</t>
+          <t>5370270</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5715919</t>
+          <t>5522408</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>75,99%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3458718</t>
+          <t>3531669</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3458718</t>
+          <t>3531669</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3458718</t>
+          <t>3531669</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3711020</t>
+          <t>3735709</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3711020</t>
+          <t>3735709</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3711020</t>
+          <t>3735709</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7169738</t>
+          <t>7267378</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7169738</t>
+          <t>7267378</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7169738</t>
+          <t>7267378</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
